--- a/SQL/Transactions Analysis/pcbanking.xlsx
+++ b/SQL/Transactions Analysis/pcbanking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\SQL\Transactions Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153E7860-B81E-45B1-8EAC-3424C4D2F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CEA9E8-FA20-489B-8CBC-58BAACDBA5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pcbanking" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8746" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9049" uniqueCount="651">
   <si>
     <t>-</t>
   </si>
@@ -1940,6 +1940,39 @@
   </si>
   <si>
     <t xml:space="preserve">Fpos Mark'S The Spot     Beech </t>
+  </si>
+  <si>
+    <t>abm deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fpos Snooty Fox Unb      Frede </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snooty Fox Unb           Frede </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wingo'S Restaurant       Woods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fpos Dairy Queen #12176  Frede </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fpos Mcdonald'S #1808    Frede </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fpos Wendy'S 6720        Monct </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnb #025                 River </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gcds625 Bristol          Brist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fpos Dairy Queen #12074  Saint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dairy Queen #12074       Saint </t>
   </si>
 </sst>
 </file>
@@ -2803,7 +2836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2972"/>
+  <dimension ref="A1:F3073"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
@@ -57487,6 +57520,1723 @@
         <v>575</v>
       </c>
     </row>
+    <row r="2973" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2973" s="6">
+        <v>45968</v>
+      </c>
+      <c r="B2973" s="2">
+        <v>-250</v>
+      </c>
+      <c r="C2973" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2973" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2973" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2974" s="6">
+        <v>45969</v>
+      </c>
+      <c r="B2974" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C2974" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2974" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2974" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2975" s="6">
+        <v>45973</v>
+      </c>
+      <c r="B2975" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C2975" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2975" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2975" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2976" s="6">
+        <v>45974</v>
+      </c>
+      <c r="B2976" s="2">
+        <v>1587.11</v>
+      </c>
+      <c r="C2976" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2976" t="s">
+        <v>621</v>
+      </c>
+      <c r="E2976" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2977" s="6">
+        <v>45975</v>
+      </c>
+      <c r="B2977" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C2977" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2977" t="s">
+        <v>622</v>
+      </c>
+      <c r="E2977" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2978" s="6">
+        <v>45978</v>
+      </c>
+      <c r="B2978" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C2978" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2978" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2978" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2979" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B2979" s="2">
+        <v>-184</v>
+      </c>
+      <c r="C2979" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2979" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2979" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2980" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B2980" s="2">
+        <v>-140</v>
+      </c>
+      <c r="C2980" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2980" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2980" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2981" s="6">
+        <v>45980</v>
+      </c>
+      <c r="B2981" s="2">
+        <v>-200</v>
+      </c>
+      <c r="C2981" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2981" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2981" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2982" s="6">
+        <v>45981</v>
+      </c>
+      <c r="B2982" s="2">
+        <v>-500</v>
+      </c>
+      <c r="C2982" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2982" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2982" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2983" s="6">
+        <v>45985</v>
+      </c>
+      <c r="B2983" s="2">
+        <v>-144.72</v>
+      </c>
+      <c r="C2983" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2983" t="s">
+        <v>625</v>
+      </c>
+      <c r="E2983" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2984" s="6">
+        <v>45985</v>
+      </c>
+      <c r="B2984" s="2">
+        <v>-175</v>
+      </c>
+      <c r="C2984" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2984" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2984" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2985" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B2985" s="2">
+        <v>110</v>
+      </c>
+      <c r="C2985" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2985" t="s">
+        <v>640</v>
+      </c>
+      <c r="E2985" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2986" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B2986" s="2">
+        <v>261.08999999999997</v>
+      </c>
+      <c r="C2986" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2986" t="s">
+        <v>629</v>
+      </c>
+      <c r="E2986" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2987" s="6">
+        <v>45987</v>
+      </c>
+      <c r="B2987" s="2">
+        <v>-150</v>
+      </c>
+      <c r="C2987" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2987" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2987" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2988" s="6">
+        <v>45988</v>
+      </c>
+      <c r="B2988" s="2">
+        <v>-175</v>
+      </c>
+      <c r="C2988" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2988" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2988" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2989" s="6">
+        <v>45988</v>
+      </c>
+      <c r="B2989" s="2">
+        <v>1587.11</v>
+      </c>
+      <c r="C2989" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2989" t="s">
+        <v>621</v>
+      </c>
+      <c r="E2989" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2990" s="6">
+        <v>45989</v>
+      </c>
+      <c r="B2990" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C2990" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2990" t="s">
+        <v>622</v>
+      </c>
+      <c r="E2990" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2991" s="6">
+        <v>45990</v>
+      </c>
+      <c r="B2991" s="2">
+        <v>-16.95</v>
+      </c>
+      <c r="C2991" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2991" t="s">
+        <v>627</v>
+      </c>
+      <c r="E2991" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2992" s="6">
+        <v>45990</v>
+      </c>
+      <c r="B2992" s="2">
+        <v>-75</v>
+      </c>
+      <c r="C2992" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2992" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2992" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2993" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B2993" s="2">
+        <v>-600</v>
+      </c>
+      <c r="C2993" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2993" t="s">
+        <v>626</v>
+      </c>
+      <c r="E2993" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2994" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B2994" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C2994" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2994" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2994" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2995" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B2995" s="2">
+        <v>150</v>
+      </c>
+      <c r="C2995" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2995" t="s">
+        <v>640</v>
+      </c>
+      <c r="E2995" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2996" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B2996" s="2">
+        <v>-13.81</v>
+      </c>
+      <c r="C2996" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2996" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2996" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2997" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B2997" s="2">
+        <v>-13.81</v>
+      </c>
+      <c r="C2997" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2997" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2997" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2998" s="6">
+        <v>45995</v>
+      </c>
+      <c r="B2998" s="2">
+        <v>-161</v>
+      </c>
+      <c r="C2998" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2998" t="s">
+        <v>619</v>
+      </c>
+      <c r="E2998" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2999" s="6">
+        <v>45996</v>
+      </c>
+      <c r="B2999" s="2">
+        <v>-125</v>
+      </c>
+      <c r="C2999" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2999" t="s">
+        <v>624</v>
+      </c>
+      <c r="E2999" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3000" s="6">
+        <v>45999</v>
+      </c>
+      <c r="B3000" s="2">
+        <v>-850</v>
+      </c>
+      <c r="C3000" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3000" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3000" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3001" s="6">
+        <v>45999</v>
+      </c>
+      <c r="B3001" s="2">
+        <v>850</v>
+      </c>
+      <c r="C3001" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3001" t="s">
+        <v>629</v>
+      </c>
+      <c r="E3001" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3002" s="6">
+        <v>46002</v>
+      </c>
+      <c r="B3002" s="2">
+        <v>-150</v>
+      </c>
+      <c r="C3002" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3002" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3002" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3003" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3003" s="6">
+        <v>46002</v>
+      </c>
+      <c r="B3003" s="2">
+        <v>1436.98</v>
+      </c>
+      <c r="C3003" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3003" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3003" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3004" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3004" s="6">
+        <v>46003</v>
+      </c>
+      <c r="B3004" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3004" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3004" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3004" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3005" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3005" s="6">
+        <v>46004</v>
+      </c>
+      <c r="B3005" s="2">
+        <v>-248.69</v>
+      </c>
+      <c r="C3005" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3005" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3005" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3006" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3006" s="6">
+        <v>46006</v>
+      </c>
+      <c r="B3006" s="2">
+        <v>-200</v>
+      </c>
+      <c r="C3006" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3006" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3006" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3007" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3007" s="6">
+        <v>46006</v>
+      </c>
+      <c r="B3007" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C3007" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3007" t="s">
+        <v>623</v>
+      </c>
+      <c r="E3007" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3008" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B3008" s="2">
+        <v>-18.940000000000001</v>
+      </c>
+      <c r="C3008" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3008" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3008" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3009" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B3009" s="2">
+        <v>-200</v>
+      </c>
+      <c r="C3009" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3009" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3009" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="3010" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3010" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B3010" s="2">
+        <v>-140</v>
+      </c>
+      <c r="C3010" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3010" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3010" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3011" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B3011" s="2">
+        <v>-184</v>
+      </c>
+      <c r="C3011" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3011" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3011" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3012" s="6">
+        <v>46009</v>
+      </c>
+      <c r="B3012" s="2">
+        <v>-25</v>
+      </c>
+      <c r="C3012" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3012" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3012" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3013" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B3013" s="2">
+        <v>-144.72</v>
+      </c>
+      <c r="C3013" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3013" t="s">
+        <v>625</v>
+      </c>
+      <c r="E3013" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3014" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B3014" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3014" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3014" t="s">
+        <v>629</v>
+      </c>
+      <c r="E3014" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3015" s="6">
+        <v>46015</v>
+      </c>
+      <c r="B3015" s="2">
+        <v>-140</v>
+      </c>
+      <c r="C3015" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3015" t="s">
+        <v>623</v>
+      </c>
+      <c r="E3015" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3016" s="6">
+        <v>46015</v>
+      </c>
+      <c r="B3016" s="2">
+        <v>1436.99</v>
+      </c>
+      <c r="C3016" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3016" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3016" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3017" s="6">
+        <v>46020</v>
+      </c>
+      <c r="B3017" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3017" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3017" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3017" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3018" s="6">
+        <v>46022</v>
+      </c>
+      <c r="B3018" s="2">
+        <v>-600</v>
+      </c>
+      <c r="C3018" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3018" t="s">
+        <v>626</v>
+      </c>
+      <c r="E3018" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3019" s="6">
+        <v>46022</v>
+      </c>
+      <c r="B3019" s="2">
+        <v>-16.95</v>
+      </c>
+      <c r="C3019" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3019" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3019" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3020" s="6">
+        <v>46022</v>
+      </c>
+      <c r="B3020" s="2">
+        <v>-125</v>
+      </c>
+      <c r="C3020" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3020" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3020" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3021" s="6">
+        <v>46027</v>
+      </c>
+      <c r="B3021" s="2">
+        <v>-110</v>
+      </c>
+      <c r="C3021" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3021" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3021" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3022" s="6">
+        <v>46030</v>
+      </c>
+      <c r="B3022" s="2">
+        <v>-12.86</v>
+      </c>
+      <c r="C3022" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3022" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3022" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3023" s="6">
+        <v>46030</v>
+      </c>
+      <c r="B3023" s="2">
+        <v>-120</v>
+      </c>
+      <c r="C3023" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3023" t="s">
+        <v>623</v>
+      </c>
+      <c r="E3023" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3024" s="6">
+        <v>46030</v>
+      </c>
+      <c r="B3024" s="2">
+        <v>-175</v>
+      </c>
+      <c r="C3024" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3024" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3024" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3025" s="6">
+        <v>46030</v>
+      </c>
+      <c r="B3025" s="2">
+        <v>1441.66</v>
+      </c>
+      <c r="C3025" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3025" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3025" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3026" s="6">
+        <v>46031</v>
+      </c>
+      <c r="B3026" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3026" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3026" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3026" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3027" s="6">
+        <v>46032</v>
+      </c>
+      <c r="B3027" s="2">
+        <v>-50</v>
+      </c>
+      <c r="C3027" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3027" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3027" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3028" s="6">
+        <v>46034</v>
+      </c>
+      <c r="B3028" s="2">
+        <v>-125</v>
+      </c>
+      <c r="C3028" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3028" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3028" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3029" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B3029" s="2">
+        <v>-75</v>
+      </c>
+      <c r="C3029" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3029" t="s">
+        <v>623</v>
+      </c>
+      <c r="E3029" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3030" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B3030" s="2">
+        <v>-125</v>
+      </c>
+      <c r="C3030" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3030" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3030" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3031" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B3031" s="2">
+        <v>-4.45</v>
+      </c>
+      <c r="C3031" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3031" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3031" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3032" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B3032" s="2">
+        <v>-4.45</v>
+      </c>
+      <c r="C3032" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3032" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3032" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3033" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B3033" s="2">
+        <v>-25.5</v>
+      </c>
+      <c r="C3033" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3033" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3033" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3034" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B3034" s="2">
+        <v>-40</v>
+      </c>
+      <c r="C3034" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3034" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3034" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3035" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B3035" s="2">
+        <v>-234</v>
+      </c>
+      <c r="C3035" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3035" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3035" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3036" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B3036" s="2">
+        <v>-50</v>
+      </c>
+      <c r="C3036" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3036" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3036" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3037" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B3037" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C3037" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3037" t="s">
+        <v>629</v>
+      </c>
+      <c r="E3037" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3038" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B3038" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3038" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3038" t="s">
+        <v>629</v>
+      </c>
+      <c r="E3038" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3039" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B3039" s="2">
+        <v>-50</v>
+      </c>
+      <c r="C3039" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3039" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3039" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3040" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B3040" s="2">
+        <v>-144.72</v>
+      </c>
+      <c r="C3040" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3040" t="s">
+        <v>625</v>
+      </c>
+      <c r="E3040" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3041" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B3041" s="2">
+        <v>-75</v>
+      </c>
+      <c r="C3041" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3041" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3041" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3042" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B3042" s="2">
+        <v>1741.9</v>
+      </c>
+      <c r="C3042" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3042" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3042" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3043" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B3043" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3043" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3043" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3043" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3044" s="6">
+        <v>46046</v>
+      </c>
+      <c r="B3044" s="2">
+        <v>-120</v>
+      </c>
+      <c r="C3044" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3044" t="s">
+        <v>623</v>
+      </c>
+      <c r="E3044" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3045" s="6">
+        <v>46046</v>
+      </c>
+      <c r="B3045" s="2">
+        <v>-120</v>
+      </c>
+      <c r="C3045" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3045" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3045" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3046" s="6">
+        <v>46053</v>
+      </c>
+      <c r="B3046" s="2">
+        <v>-16.95</v>
+      </c>
+      <c r="C3046" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3046" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3046" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3047" s="6">
+        <v>46055</v>
+      </c>
+      <c r="B3047" s="2">
+        <v>-600</v>
+      </c>
+      <c r="C3047" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3047" t="s">
+        <v>626</v>
+      </c>
+      <c r="E3047" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3048" s="6">
+        <v>46055</v>
+      </c>
+      <c r="B3048" s="2">
+        <v>-80</v>
+      </c>
+      <c r="C3048" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3048" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3048" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3049" s="6">
+        <v>46055</v>
+      </c>
+      <c r="B3049" s="2">
+        <v>50</v>
+      </c>
+      <c r="C3049" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3049" t="s">
+        <v>629</v>
+      </c>
+      <c r="E3049" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3050" s="6">
+        <v>46056</v>
+      </c>
+      <c r="B3050" s="2">
+        <v>-40</v>
+      </c>
+      <c r="C3050" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3050" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3050" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3051" s="6">
+        <v>46057</v>
+      </c>
+      <c r="B3051" s="2">
+        <v>-161</v>
+      </c>
+      <c r="C3051" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3051" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3051" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3052" s="6">
+        <v>46058</v>
+      </c>
+      <c r="B3052" s="2">
+        <v>-29</v>
+      </c>
+      <c r="C3052" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3052" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3052" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3053" s="6">
+        <v>46058</v>
+      </c>
+      <c r="B3053" s="2">
+        <v>-204</v>
+      </c>
+      <c r="C3053" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3053" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3053" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3054" s="6">
+        <v>46058</v>
+      </c>
+      <c r="B3054" s="2">
+        <v>-200</v>
+      </c>
+      <c r="C3054" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3054" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3054" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3055" s="6">
+        <v>46058</v>
+      </c>
+      <c r="B3055" s="2">
+        <v>-110</v>
+      </c>
+      <c r="C3055" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3055" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3055" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3056" s="6">
+        <v>46058</v>
+      </c>
+      <c r="B3056" s="2">
+        <v>1591.78</v>
+      </c>
+      <c r="C3056" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3056" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3056" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3057" s="6">
+        <v>46059</v>
+      </c>
+      <c r="B3057" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3057" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3057" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3057" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3058" s="6">
+        <v>46059</v>
+      </c>
+      <c r="B3058" s="2">
+        <v>-150</v>
+      </c>
+      <c r="C3058" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3058" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3058" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3059" s="6">
+        <v>46066</v>
+      </c>
+      <c r="B3059" s="2">
+        <v>-125</v>
+      </c>
+      <c r="C3059" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3059" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3059" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3060" s="6">
+        <v>46070</v>
+      </c>
+      <c r="B3060" s="2">
+        <v>-75</v>
+      </c>
+      <c r="C3060" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3060" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3060" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3061" s="6">
+        <v>46072</v>
+      </c>
+      <c r="B3061" s="2">
+        <v>1591.78</v>
+      </c>
+      <c r="C3061" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3061" t="s">
+        <v>621</v>
+      </c>
+      <c r="E3061" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3062" s="6">
+        <v>46073</v>
+      </c>
+      <c r="B3062" s="2">
+        <v>-366.69</v>
+      </c>
+      <c r="C3062" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3062" t="s">
+        <v>622</v>
+      </c>
+      <c r="E3062" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3063" s="6">
+        <v>46074</v>
+      </c>
+      <c r="B3063" s="2">
+        <v>-6.31</v>
+      </c>
+      <c r="C3063" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3063" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3063" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3064" s="6">
+        <v>46074</v>
+      </c>
+      <c r="B3064" s="2">
+        <v>-16.66</v>
+      </c>
+      <c r="C3064" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3064" t="s">
+        <v>619</v>
+      </c>
+      <c r="E3064" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3065" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B3065" s="2">
+        <v>-144.72</v>
+      </c>
+      <c r="C3065" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3065" t="s">
+        <v>625</v>
+      </c>
+      <c r="E3065" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3066" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B3066" s="2">
+        <v>-150</v>
+      </c>
+      <c r="C3066" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3066" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3066" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3067" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B3067" s="2">
+        <v>-200</v>
+      </c>
+      <c r="C3067" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3067" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3067" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3068" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B3068" s="2">
+        <v>-275</v>
+      </c>
+      <c r="C3068" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3068" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3068" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3069" s="6">
+        <v>46078</v>
+      </c>
+      <c r="B3069" s="2">
+        <v>-50</v>
+      </c>
+      <c r="C3069" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3069" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3069" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3070" s="6">
+        <v>46079</v>
+      </c>
+      <c r="B3070" s="2">
+        <v>-25</v>
+      </c>
+      <c r="C3070" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3070" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3070" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3071" s="6">
+        <v>46081</v>
+      </c>
+      <c r="B3071" s="2">
+        <v>-16.95</v>
+      </c>
+      <c r="C3071" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3071" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3071" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3072" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B3072" s="2">
+        <v>-600</v>
+      </c>
+      <c r="C3072" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3072" t="s">
+        <v>626</v>
+      </c>
+      <c r="E3072" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3073" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B3073" s="2">
+        <v>-100</v>
+      </c>
+      <c r="C3073" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3073" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3073" t="s">
+        <v>616</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
